--- a/Document/300_DUYDキャラクター仕様.xlsx
+++ b/Document/300_DUYDキャラクター仕様.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\新しいフォルダー\Document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10AB9B4D-31B7-4503-8FD2-8538F66BF526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C55676E-DE0F-4333-B05B-12BDBCB44C5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{A7C1605A-4F8D-422A-A50A-47C3F46D6375}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{A7C1605A-4F8D-422A-A50A-47C3F46D6375}"/>
   </bookViews>
   <sheets>
     <sheet name="更新履歴" sheetId="2" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="146">
   <si>
     <t>更新履歴</t>
     <rPh sb="0" eb="4">
@@ -1628,6 +1628,23 @@
     </rPh>
     <rPh sb="6" eb="10">
       <t>シヨウツイカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>・10秒ごとに1減少</t>
+    <rPh sb="3" eb="4">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ゲンショウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1減少</t>
+    <rPh sb="1" eb="3">
+      <t>ゲンショウ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -1938,8 +1955,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="3695700" y="8591550"/>
-          <a:ext cx="3395663" cy="1671638"/>
+          <a:off x="3689985" y="8591550"/>
+          <a:ext cx="3355658" cy="1671638"/>
           <a:chOff x="3681413" y="8677275"/>
           <a:chExt cx="3295650" cy="1671638"/>
         </a:xfrm>
@@ -2572,8 +2589,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="7339012" y="8605838"/>
-          <a:ext cx="3915594" cy="600179"/>
+          <a:off x="7289482" y="8605838"/>
+          <a:ext cx="3869874" cy="600179"/>
           <a:chOff x="8767763" y="5857875"/>
           <a:chExt cx="3801294" cy="600179"/>
         </a:xfrm>
@@ -3535,6 +3552,106 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>121920</xdr:colOff>
+      <xdr:row>92</xdr:row>
+      <xdr:rowOff>60960</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
+      <xdr:row>92</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="7" name="直線コネクタ 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D1975550-DC65-4F41-9380-7DB9F2D6B576}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="4686300" y="14081760"/>
+          <a:ext cx="1333500" cy="15240"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
+      <xdr:row>93</xdr:row>
+      <xdr:rowOff>68580</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>121920</xdr:colOff>
+      <xdr:row>93</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="19" name="直線コネクタ 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{540582C7-B733-43CB-908E-7CA7E5FC8477}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="6515100" y="14241780"/>
+          <a:ext cx="411480" cy="7620"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -3836,21 +3953,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E2D295A-9295-46AC-88E4-F7ADF9D99499}">
   <dimension ref="B1:H6"/>
-  <sheetFormatPr defaultColWidth="2.125" defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.7"/>
+  <sheetFormatPr defaultColWidth="2.09765625" defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="5" max="5" width="16.1875" customWidth="1"/>
-    <col min="6" max="6" width="7.3125" customWidth="1"/>
+    <col min="5" max="5" width="16.19921875" customWidth="1"/>
+    <col min="6" max="6" width="7.296875" customWidth="1"/>
     <col min="7" max="7" width="21.5" customWidth="1"/>
-    <col min="8" max="8" width="15.125" customWidth="1"/>
+    <col min="8" max="8" width="15.09765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" s="1" customFormat="1" ht="32.25" x14ac:dyDescent="0.7">
+    <row r="1" spans="2:8" s="1" customFormat="1" ht="32.4" x14ac:dyDescent="0.45">
       <c r="B1" s="3"/>
       <c r="E1" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="4" spans="2:8" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="E4" s="5" t="s">
         <v>3</v>
       </c>
@@ -3864,7 +3981,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="5" spans="2:8" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="E5" s="20">
         <v>46066</v>
       </c>
@@ -3878,7 +3995,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="6" spans="2:8" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="E6" s="20">
         <v>46073</v>
       </c>
@@ -3901,14 +4018,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFD89370-1DE1-4DF5-942C-CF8F59DF7864}">
-  <dimension ref="A1:W281"/>
-  <sheetFormatPr defaultColWidth="2.125" defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.7"/>
+  <dimension ref="A1:AA281"/>
+  <sheetFormatPr defaultColWidth="2.09765625" defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
     <col min="2" max="2" width="20" style="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="6" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="1" spans="1:6" s="6" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3919,278 +4036,284 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:6" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="3" spans="1:6" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B3" s="11"/>
       <c r="D3" s="10" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="5" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="E5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:6" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="7" spans="1:6" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B7" s="11"/>
       <c r="D7" s="10" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="9" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="D9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="10" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="D10" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:6" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="12" spans="1:6" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B12" s="11"/>
       <c r="D12" s="10" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:6" s="12" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="14" spans="1:6" s="12" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B14" s="13"/>
       <c r="C14" s="14"/>
       <c r="E14" s="12" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="16" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="F16" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="7:7" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="18" spans="7:7" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="G18" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="40" spans="5:7" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="40" spans="5:7" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="F40" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="42" spans="5:7" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="42" spans="5:7" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="G42" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="43" spans="5:7" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="43" spans="5:7" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="G43" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="44" spans="5:7" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="44" spans="5:7" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="G44" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="45" spans="5:7" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="45" spans="5:7" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="G45" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="47" spans="5:7" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="47" spans="5:7" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="E47" s="15" t="s">
         <v>21</v>
       </c>
       <c r="F47" s="15"/>
     </row>
-    <row r="49" spans="5:7" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="49" spans="5:7" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="F49" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="50" spans="5:7" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="50" spans="5:7" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="G50" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="52" spans="5:7" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="52" spans="5:7" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="E52" s="15" t="s">
         <v>34</v>
       </c>
       <c r="F52" s="15"/>
     </row>
-    <row r="54" spans="5:7" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="54" spans="5:7" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="F54" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="56" spans="5:7" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="56" spans="5:7" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="F56" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="69" spans="6:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="69" spans="6:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="F69" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="71" spans="6:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="71" spans="6:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="H71" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="74" spans="6:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="74" spans="6:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="H74" s="16" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="76" spans="6:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="76" spans="6:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I76" s="17" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="78" spans="6:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="78" spans="6:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="J78" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="80" spans="6:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="80" spans="6:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="J80" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="82" spans="9:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="82" spans="9:27" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="J82" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="84" spans="9:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="84" spans="9:27" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="K84" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="86" spans="9:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="86" spans="9:27" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I86" s="17" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="88" spans="9:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="88" spans="9:27" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="J88" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="89" spans="9:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="89" spans="9:27" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="K89" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="91" spans="9:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="91" spans="9:27" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="L91" s="16" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="93" spans="9:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="93" spans="9:27" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="M93" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="94" spans="9:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="V93" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="94" spans="9:27" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="M94" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="95" spans="9:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="AA94" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="95" spans="9:27" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="M95" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="97" spans="9:12" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="97" spans="9:12" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="K97" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="99" spans="9:12" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="99" spans="9:12" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="L99" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="101" spans="9:12" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="101" spans="9:12" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="J101" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="103" spans="9:12" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="103" spans="9:12" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I103" s="16" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="105" spans="9:12" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="105" spans="9:12" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="J105" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="107" spans="9:12" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="107" spans="9:12" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="K107" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="109" spans="9:12" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="109" spans="9:12" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="K109" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="111" spans="9:12" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="111" spans="9:12" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="L111" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="113" spans="9:22" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="113" spans="9:22" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I113" s="16" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="114" spans="9:22" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="114" spans="9:22" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I114" s="16"/>
     </row>
-    <row r="115" spans="9:22" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="115" spans="9:22" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I115" s="16"/>
       <c r="J115" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="116" spans="9:22" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="116" spans="9:22" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I116" s="16"/>
     </row>
-    <row r="117" spans="9:22" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="117" spans="9:22" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I117" s="16"/>
       <c r="K117" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="118" spans="9:22" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="118" spans="9:22" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I118" s="16"/>
     </row>
-    <row r="119" spans="9:22" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="119" spans="9:22" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="K119" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="121" spans="9:22" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="121" spans="9:22" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="K121" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="122" spans="9:22" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="122" spans="9:22" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="L122" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="124" spans="9:22" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="124" spans="9:22" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I124" s="16" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="125" spans="9:22" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="125" spans="9:22" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I125" s="16"/>
     </row>
-    <row r="126" spans="9:22" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="126" spans="9:22" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I126" t="s">
         <v>42</v>
       </c>
@@ -4198,7 +4321,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="127" spans="9:22" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="127" spans="9:22" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="J127" t="s">
         <v>115</v>
       </c>
@@ -4206,7 +4329,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="128" spans="9:22" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="128" spans="9:22" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I128" t="s">
         <v>116</v>
       </c>
@@ -4214,7 +4337,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="129" spans="5:22" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="129" spans="5:22" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="J129" t="s">
         <v>43</v>
       </c>
@@ -4222,7 +4345,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="131" spans="5:22" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="131" spans="5:22" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I131" t="s">
         <v>47</v>
       </c>
@@ -4230,7 +4353,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="132" spans="5:22" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="132" spans="5:22" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="J132" t="s">
         <v>49</v>
       </c>
@@ -4238,7 +4361,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="133" spans="5:22" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="133" spans="5:22" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I133" t="s">
         <v>118</v>
       </c>
@@ -4246,7 +4369,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="134" spans="5:22" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="134" spans="5:22" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="J134" t="s">
         <v>50</v>
       </c>
@@ -4254,94 +4377,94 @@
         <v>52</v>
       </c>
     </row>
-    <row r="136" spans="5:22" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="136" spans="5:22" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="G136" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="138" spans="5:22" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="138" spans="5:22" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="G138" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="144" spans="5:22" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="144" spans="5:22" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="E144" s="15" t="s">
         <v>24</v>
       </c>
       <c r="F144" s="15"/>
     </row>
-    <row r="146" spans="5:8" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="146" spans="5:8" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="F146" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="147" spans="5:8" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="147" spans="5:8" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="G147" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="149" spans="5:8" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="149" spans="5:8" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="G149" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="151" spans="5:8" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="151" spans="5:8" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="H151" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="153" spans="5:8" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="153" spans="5:8" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="G153" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="154" spans="5:8" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="154" spans="5:8" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="H154" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="158" spans="5:8" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="158" spans="5:8" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="E158" s="15" t="s">
         <v>29</v>
       </c>
       <c r="F158" s="15"/>
     </row>
-    <row r="160" spans="5:8" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="160" spans="5:8" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="F160" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="162" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="162" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="G162" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="164" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="164" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I164" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="165" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="165" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="J165" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="167" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="167" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="G167" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="168" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="168" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="H168" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="170" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="170" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I170" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="171" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="171" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A171" s="20">
         <v>46073</v>
       </c>
@@ -4352,39 +4475,39 @@
         <v>140</v>
       </c>
     </row>
-    <row r="173" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="173" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="E173" s="16" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="175" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="175" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="F175" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="177" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="177" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="G177" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="180" spans="2:7" s="12" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="180" spans="2:7" s="12" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B180" s="13"/>
       <c r="C180" s="14"/>
       <c r="E180" s="12" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="182" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="182" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="E182" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="184" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="184" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="E184" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="200" spans="6:23" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="200" spans="6:23" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="G200" t="s">
         <v>59</v>
       </c>
@@ -4404,57 +4527,57 @@
         <v>64</v>
       </c>
     </row>
-    <row r="203" spans="6:23" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="203" spans="6:23" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="F203" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="205" spans="6:23" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="205" spans="6:23" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="G205" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="207" spans="6:23" ht="12.75" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="207" spans="6:23" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="H207" s="16" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="208" spans="6:23" ht="12.75" customHeight="1" x14ac:dyDescent="0.7"/>
-    <row r="209" spans="6:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="208" spans="6:23" ht="12.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="209" spans="6:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I209" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="210" spans="6:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.7"/>
-    <row r="211" spans="6:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="210" spans="6:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="211" spans="6:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="J211" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="212" spans="6:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.7"/>
-    <row r="213" spans="6:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="212" spans="6:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="213" spans="6:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="J213" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="214" spans="6:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.7"/>
-    <row r="215" spans="6:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.7"/>
-    <row r="216" spans="6:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="214" spans="6:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="215" spans="6:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="216" spans="6:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="H216" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="218" spans="6:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="218" spans="6:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I218" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="220" spans="6:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="220" spans="6:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="J220" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="224" spans="6:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="224" spans="6:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="F224" s="15" t="s">
         <v>66</v>
       </c>
@@ -4464,12 +4587,12 @@
       <c r="J224" s="15"/>
       <c r="K224" s="15"/>
     </row>
-    <row r="226" spans="7:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="226" spans="7:13" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="G226" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="228" spans="7:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="228" spans="7:13" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="H228" t="s">
         <v>68</v>
       </c>
@@ -4477,7 +4600,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="229" spans="7:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="229" spans="7:13" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="H229" t="s">
         <v>70</v>
       </c>
@@ -4485,7 +4608,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="230" spans="7:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="230" spans="7:13" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="H230" t="s">
         <v>69</v>
       </c>
@@ -4493,137 +4616,137 @@
         <v>79</v>
       </c>
     </row>
-    <row r="233" spans="7:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="233" spans="7:13" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="G233" s="15" t="s">
         <v>71</v>
       </c>
       <c r="H233" s="15"/>
     </row>
-    <row r="235" spans="7:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="235" spans="7:13" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="H235" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="237" spans="7:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="237" spans="7:13" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I237" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="239" spans="7:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="239" spans="7:13" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I239" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="240" spans="7:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="240" spans="7:13" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I240" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="242" spans="7:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="242" spans="7:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I242" s="16" t="s">
         <v>76</v>
       </c>
       <c r="J242" s="16"/>
       <c r="K242" s="16"/>
     </row>
-    <row r="244" spans="7:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="244" spans="7:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="J244" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="246" spans="7:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="246" spans="7:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="J246" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="247" spans="7:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="247" spans="7:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="J247" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="249" spans="7:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="249" spans="7:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="G249" s="15" t="s">
         <v>82</v>
       </c>
       <c r="H249" s="15"/>
     </row>
-    <row r="251" spans="7:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="251" spans="7:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="H251" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="253" spans="7:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="253" spans="7:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I253" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="255" spans="7:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="255" spans="7:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I255" s="16" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="257" spans="7:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="257" spans="7:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="J257" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="259" spans="7:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="259" spans="7:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="J259" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="260" spans="7:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="260" spans="7:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="J260" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="262" spans="7:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="262" spans="7:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="G262" s="15" t="s">
         <v>120</v>
       </c>
       <c r="H262" s="15"/>
     </row>
-    <row r="264" spans="7:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="264" spans="7:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="H264" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="266" spans="7:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="266" spans="7:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I266" s="16" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="268" spans="7:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="268" spans="7:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="J268" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="270" spans="7:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="270" spans="7:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="J270" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="271" spans="7:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="271" spans="7:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="J271" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="274" spans="2:8" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="274" spans="2:8" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="F274" s="16" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="276" spans="2:8" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="276" spans="2:8" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="G276" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="278" spans="2:8" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="278" spans="2:8" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="H278" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="281" spans="2:8" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="281" spans="2:8" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B281" s="18"/>
       <c r="D281" s="19" t="s">
         <v>136</v>

--- a/Document/300_DUYDキャラクター仕様.xlsx
+++ b/Document/300_DUYDキャラクター仕様.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\新しいフォルダー\Document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C55676E-DE0F-4333-B05B-12BDBCB44C5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{421F171B-310A-483A-AC04-F3A7C175E2ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{A7C1605A-4F8D-422A-A50A-47C3F46D6375}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{A7C1605A-4F8D-422A-A50A-47C3F46D6375}"/>
   </bookViews>
   <sheets>
     <sheet name="更新履歴" sheetId="2" r:id="rId1"/>
@@ -1461,10 +1461,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>A＝１×0.2n</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>キャラクターがダメージを受けたとき</t>
     <rPh sb="12" eb="13">
       <t>ウ</t>
@@ -1646,6 +1642,10 @@
     <rPh sb="1" eb="3">
       <t>ゲンショウ</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>A＝0.2n</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -1955,8 +1955,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="3689985" y="8591550"/>
-          <a:ext cx="3355658" cy="1671638"/>
+          <a:off x="3695700" y="8591550"/>
+          <a:ext cx="3395663" cy="1671638"/>
           <a:chOff x="3681413" y="8677275"/>
           <a:chExt cx="3295650" cy="1671638"/>
         </a:xfrm>
@@ -2589,8 +2589,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="7289482" y="8605838"/>
-          <a:ext cx="3869874" cy="600179"/>
+          <a:off x="7339012" y="8605838"/>
+          <a:ext cx="3915594" cy="600179"/>
           <a:chOff x="8767763" y="5857875"/>
           <a:chExt cx="3801294" cy="600179"/>
         </a:xfrm>
@@ -3953,21 +3953,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E2D295A-9295-46AC-88E4-F7ADF9D99499}">
   <dimension ref="B1:H6"/>
-  <sheetFormatPr defaultColWidth="2.09765625" defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="2.125" defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.7"/>
   <cols>
-    <col min="5" max="5" width="16.19921875" customWidth="1"/>
-    <col min="6" max="6" width="7.296875" customWidth="1"/>
+    <col min="5" max="5" width="16.1875" customWidth="1"/>
+    <col min="6" max="6" width="7.3125" customWidth="1"/>
     <col min="7" max="7" width="21.5" customWidth="1"/>
-    <col min="8" max="8" width="15.09765625" customWidth="1"/>
+    <col min="8" max="8" width="15.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" s="1" customFormat="1" ht="32.4" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:8" s="1" customFormat="1" ht="32.25" x14ac:dyDescent="0.7">
       <c r="B1" s="3"/>
       <c r="E1" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:8" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="E4" s="5" t="s">
         <v>3</v>
       </c>
@@ -3981,32 +3981,32 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:8" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="E5" s="20">
         <v>46066</v>
       </c>
       <c r="F5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G5" t="s">
         <v>7</v>
       </c>
       <c r="H5" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="6" spans="2:8" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="E6" s="20">
         <v>46073</v>
       </c>
       <c r="F6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G6" t="s">
         <v>7</v>
       </c>
       <c r="H6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -4019,13 +4019,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFD89370-1DE1-4DF5-942C-CF8F59DF7864}">
   <dimension ref="A1:AA281"/>
-  <sheetFormatPr defaultColWidth="2.09765625" defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="2.125" defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.7"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
     <col min="2" max="2" width="20" style="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="6" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" s="6" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -4036,284 +4036,284 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:6" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:6" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="B3" s="11"/>
       <c r="D3" s="10" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="E5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:6" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:6" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="B7" s="11"/>
       <c r="D7" s="10" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="D9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="D10" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:6" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:6" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="B12" s="11"/>
       <c r="D12" s="10" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:6" s="12" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:6" s="12" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="B14" s="13"/>
       <c r="C14" s="14"/>
       <c r="E14" s="12" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="F16" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="7:7" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="7:7" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="G18" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="40" spans="5:7" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="5:7" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="F40" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="42" spans="5:7" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="42" spans="5:7" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="G42" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="43" spans="5:7" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="5:7" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="G43" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="44" spans="5:7" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="44" spans="5:7" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="G44" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="45" spans="5:7" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="45" spans="5:7" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="G45" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="47" spans="5:7" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="5:7" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="E47" s="15" t="s">
         <v>21</v>
       </c>
       <c r="F47" s="15"/>
     </row>
-    <row r="49" spans="5:7" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="49" spans="5:7" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="F49" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="50" spans="5:7" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="50" spans="5:7" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="G50" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="52" spans="5:7" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="52" spans="5:7" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="E52" s="15" t="s">
         <v>34</v>
       </c>
       <c r="F52" s="15"/>
     </row>
-    <row r="54" spans="5:7" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="54" spans="5:7" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="F54" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="56" spans="5:7" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="56" spans="5:7" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="F56" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="69" spans="6:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="69" spans="6:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="F69" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="71" spans="6:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="71" spans="6:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="H71" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="74" spans="6:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="74" spans="6:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="H74" s="16" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="76" spans="6:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="76" spans="6:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="I76" s="17" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="78" spans="6:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="78" spans="6:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J78" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="80" spans="6:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="80" spans="6:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J80" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="82" spans="9:27" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="82" spans="9:27" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J82" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="84" spans="9:27" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="84" spans="9:27" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="K84" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="86" spans="9:27" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="86" spans="9:27" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="I86" s="17" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="88" spans="9:27" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="88" spans="9:27" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J88" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="89" spans="9:27" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="89" spans="9:27" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="K89" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="91" spans="9:27" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="91" spans="9:27" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="L91" s="16" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="93" spans="9:27" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="93" spans="9:27" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="M93" t="s">
         <v>97</v>
       </c>
       <c r="V93" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="94" spans="9:27" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="94" spans="9:27" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="M94" t="s">
         <v>98</v>
       </c>
       <c r="AA94" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="95" spans="9:27" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="95" spans="9:27" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="M95" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="97" spans="9:12" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="97" spans="9:12" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="K97" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="99" spans="9:12" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="99" spans="9:12" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="L99" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="101" spans="9:12" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="101" spans="9:12" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J101" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="103" spans="9:12" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="103" spans="9:12" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="I103" s="16" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="105" spans="9:12" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="105" spans="9:12" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J105" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="107" spans="9:12" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="107" spans="9:12" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="K107" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="109" spans="9:12" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="109" spans="9:12" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="K109" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="111" spans="9:12" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="111" spans="9:12" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="L111" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="113" spans="9:22" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="113" spans="9:22" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="I113" s="16" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="114" spans="9:22" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="114" spans="9:22" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="I114" s="16"/>
     </row>
-    <row r="115" spans="9:22" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="115" spans="9:22" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="I115" s="16"/>
       <c r="J115" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="116" spans="9:22" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="116" spans="9:22" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="I116" s="16"/>
     </row>
-    <row r="117" spans="9:22" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="117" spans="9:22" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="I117" s="16"/>
       <c r="K117" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="118" spans="9:22" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="118" spans="9:22" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="I118" s="16"/>
     </row>
-    <row r="119" spans="9:22" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="119" spans="9:22" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="K119" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="121" spans="9:22" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="121" spans="9:22" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="K121" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="122" spans="9:22" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="122" spans="9:22" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="L122" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="124" spans="9:22" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="124" spans="9:22" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="I124" s="16" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="125" spans="9:22" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="125" spans="9:22" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="I125" s="16"/>
     </row>
-    <row r="126" spans="9:22" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="126" spans="9:22" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="I126" t="s">
         <v>42</v>
       </c>
@@ -4321,7 +4321,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="127" spans="9:22" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="127" spans="9:22" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J127" t="s">
         <v>115</v>
       </c>
@@ -4329,7 +4329,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="128" spans="9:22" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="128" spans="9:22" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="I128" t="s">
         <v>116</v>
       </c>
@@ -4337,7 +4337,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="129" spans="5:22" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="129" spans="5:22" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J129" t="s">
         <v>43</v>
       </c>
@@ -4345,7 +4345,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="131" spans="5:22" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="131" spans="5:22" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="I131" t="s">
         <v>47</v>
       </c>
@@ -4353,7 +4353,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="132" spans="5:22" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="132" spans="5:22" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J132" t="s">
         <v>49</v>
       </c>
@@ -4361,7 +4361,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="133" spans="5:22" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="133" spans="5:22" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="I133" t="s">
         <v>118</v>
       </c>
@@ -4369,7 +4369,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="134" spans="5:22" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="134" spans="5:22" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J134" t="s">
         <v>50</v>
       </c>
@@ -4377,137 +4377,137 @@
         <v>52</v>
       </c>
     </row>
-    <row r="136" spans="5:22" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="136" spans="5:22" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="G136" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="138" spans="5:22" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="138" spans="5:22" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="G138" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="144" spans="5:22" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="144" spans="5:22" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="E144" s="15" t="s">
         <v>24</v>
       </c>
       <c r="F144" s="15"/>
     </row>
-    <row r="146" spans="5:8" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="146" spans="5:8" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="F146" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="147" spans="5:8" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="147" spans="5:8" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="G147" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="149" spans="5:8" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="149" spans="5:8" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="G149" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="151" spans="5:8" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="151" spans="5:8" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="H151" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="153" spans="5:8" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="153" spans="5:8" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="G153" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="154" spans="5:8" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="154" spans="5:8" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="H154" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="158" spans="5:8" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="158" spans="5:8" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="E158" s="15" t="s">
         <v>29</v>
       </c>
       <c r="F158" s="15"/>
     </row>
-    <row r="160" spans="5:8" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="160" spans="5:8" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="F160" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="162" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="162" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="G162" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="164" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="164" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="I164" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="165" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="J165" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="165" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="J165" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="167" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="167" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="G167" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="168" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="168" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="H168" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="170" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="170" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="I170" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="171" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="171" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A171" s="20">
         <v>46073</v>
       </c>
       <c r="B171" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="J171" t="s">
         <v>139</v>
       </c>
-      <c r="J171" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="173" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    </row>
+    <row r="173" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="E173" s="16" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="175" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="F175" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="175" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="F175" t="s">
+    <row r="177" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="G177" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="177" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="G177" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="180" spans="2:7" s="12" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="180" spans="2:7" s="12" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="B180" s="13"/>
       <c r="C180" s="14"/>
       <c r="E180" s="12" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="182" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="182" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="E182" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="184" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="184" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="E184" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="200" spans="6:23" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="200" spans="6:23" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="G200" t="s">
         <v>59</v>
       </c>
@@ -4527,57 +4527,57 @@
         <v>64</v>
       </c>
     </row>
-    <row r="203" spans="6:23" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="203" spans="6:23" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="F203" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="205" spans="6:23" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="205" spans="6:23" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="G205" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="207" spans="6:23" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="207" spans="6:23" ht="12.75" customHeight="1" x14ac:dyDescent="0.7">
       <c r="H207" s="16" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="208" spans="6:23" ht="12.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="209" spans="6:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="208" spans="6:23" ht="12.75" customHeight="1" x14ac:dyDescent="0.7"/>
+    <row r="209" spans="6:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.7">
       <c r="I209" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="210" spans="6:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="211" spans="6:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="210" spans="6:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.7"/>
+    <row r="211" spans="6:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J211" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="212" spans="6:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="213" spans="6:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="212" spans="6:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.7"/>
+    <row r="213" spans="6:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J213" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="214" spans="6:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="215" spans="6:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="216" spans="6:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="214" spans="6:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.7"/>
+    <row r="215" spans="6:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.7"/>
+    <row r="216" spans="6:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="H216" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="218" spans="6:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="218" spans="6:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="I218" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="220" spans="6:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="220" spans="6:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J220" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="224" spans="6:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="224" spans="6:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="F224" s="15" t="s">
         <v>66</v>
       </c>
@@ -4587,12 +4587,12 @@
       <c r="J224" s="15"/>
       <c r="K224" s="15"/>
     </row>
-    <row r="226" spans="7:13" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="226" spans="7:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="G226" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="228" spans="7:13" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="228" spans="7:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="H228" t="s">
         <v>68</v>
       </c>
@@ -4600,7 +4600,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="229" spans="7:13" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="229" spans="7:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="H229" t="s">
         <v>70</v>
       </c>
@@ -4608,7 +4608,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="230" spans="7:13" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="230" spans="7:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="H230" t="s">
         <v>69</v>
       </c>
@@ -4616,140 +4616,140 @@
         <v>79</v>
       </c>
     </row>
-    <row r="233" spans="7:13" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="233" spans="7:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="G233" s="15" t="s">
         <v>71</v>
       </c>
       <c r="H233" s="15"/>
     </row>
-    <row r="235" spans="7:13" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="235" spans="7:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="H235" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="237" spans="7:13" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="237" spans="7:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="I237" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="239" spans="7:13" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="239" spans="7:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="I239" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="240" spans="7:13" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="240" spans="7:13" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="I240" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="242" spans="7:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="242" spans="7:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="I242" s="16" t="s">
         <v>76</v>
       </c>
       <c r="J242" s="16"/>
       <c r="K242" s="16"/>
     </row>
-    <row r="244" spans="7:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="244" spans="7:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J244" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="246" spans="7:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="246" spans="7:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J246" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="247" spans="7:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="247" spans="7:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J247" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="249" spans="7:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="249" spans="7:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="G249" s="15" t="s">
         <v>82</v>
       </c>
       <c r="H249" s="15"/>
     </row>
-    <row r="251" spans="7:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="251" spans="7:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="H251" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="253" spans="7:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="253" spans="7:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="I253" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="255" spans="7:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="255" spans="7:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="I255" s="16" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="257" spans="7:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="257" spans="7:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J257" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="259" spans="7:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="259" spans="7:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J259" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="260" spans="7:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="260" spans="7:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J260" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="262" spans="7:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="262" spans="7:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="G262" s="15" t="s">
         <v>120</v>
       </c>
       <c r="H262" s="15"/>
     </row>
-    <row r="264" spans="7:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="264" spans="7:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="H264" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="266" spans="7:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="266" spans="7:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="I266" s="16" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="268" spans="7:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="268" spans="7:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J268" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="270" spans="7:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="270" spans="7:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J270" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="271" spans="7:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="271" spans="7:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J271" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="274" spans="2:8" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="274" spans="2:8" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="F274" s="16" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="276" spans="2:8" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="G276" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="276" spans="2:8" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="G276" t="s">
+    <row r="278" spans="2:8" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="H278" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="278" spans="2:8" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="H278" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="281" spans="2:8" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="281" spans="2:8" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="B281" s="18"/>
       <c r="D281" s="19" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>

--- a/Document/300_DUYDキャラクター仕様.xlsx
+++ b/Document/300_DUYDキャラクター仕様.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\新しいフォルダー\Document\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\新しいフォルダー (2)\Document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{421F171B-310A-483A-AC04-F3A7C175E2ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E0F3C66-13F3-465D-AB8A-851B984E8FA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{A7C1605A-4F8D-422A-A50A-47C3F46D6375}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{A7C1605A-4F8D-422A-A50A-47C3F46D6375}"/>
   </bookViews>
   <sheets>
     <sheet name="更新履歴" sheetId="2" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="149">
   <si>
     <t>更新履歴</t>
     <rPh sb="0" eb="4">
@@ -956,13 +956,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>プレイヤーの攻撃力です。</t>
-    <rPh sb="6" eb="9">
-      <t>コウゲキリョク</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>初期値は30です</t>
     <rPh sb="0" eb="3">
       <t>ショキチ</t>
@@ -1646,6 +1639,65 @@
   </si>
   <si>
     <t>A＝0.2n</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>速度追加</t>
+    <rPh sb="0" eb="2">
+      <t>ソクド</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>プレイヤーの攻撃力と</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>移動速度です</t>
+    </r>
+    <rPh sb="6" eb="9">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <rPh sb="10" eb="14">
+      <t>イドウソクド</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>既存の移動速度に加算されます</t>
+    <rPh sb="0" eb="2">
+      <t>キゾン</t>
+    </rPh>
+    <rPh sb="3" eb="7">
+      <t>イドウソクド</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>カサン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>プレイヤーの移動速度に関する仕様追加</t>
+    <rPh sb="6" eb="10">
+      <t>イドウソクド</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="14" eb="18">
+      <t>シヨウツイカ</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -3952,13 +4004,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E2D295A-9295-46AC-88E4-F7ADF9D99499}">
-  <dimension ref="B1:H6"/>
+  <dimension ref="B1:H7"/>
   <sheetFormatPr defaultColWidth="2.125" defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.7"/>
   <cols>
     <col min="5" max="5" width="16.1875" customWidth="1"/>
     <col min="6" max="6" width="7.3125" customWidth="1"/>
     <col min="7" max="7" width="21.5" customWidth="1"/>
-    <col min="8" max="8" width="15.125" customWidth="1"/>
+    <col min="8" max="8" width="34.8125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:8" s="1" customFormat="1" ht="32.25" x14ac:dyDescent="0.7">
@@ -3986,13 +4038,13 @@
         <v>46066</v>
       </c>
       <c r="F5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G5" t="s">
         <v>7</v>
       </c>
       <c r="H5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="6" spans="2:8" ht="12" customHeight="1" x14ac:dyDescent="0.7">
@@ -4000,13 +4052,27 @@
         <v>46073</v>
       </c>
       <c r="F6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G6" t="s">
         <v>7</v>
       </c>
       <c r="H6" t="s">
-        <v>142</v>
+        <v>141</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="E7" s="20">
+        <v>46105</v>
+      </c>
+      <c r="F7" t="s">
+        <v>135</v>
+      </c>
+      <c r="G7" t="s">
+        <v>7</v>
+      </c>
+      <c r="H7" t="s">
+        <v>148</v>
       </c>
     </row>
   </sheetData>
@@ -4175,12 +4241,12 @@
     </row>
     <row r="82" spans="9:27" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J82" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="84" spans="9:27" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="K84" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="86" spans="9:27" ht="12" customHeight="1" x14ac:dyDescent="0.7">
@@ -4195,78 +4261,89 @@
     </row>
     <row r="89" spans="9:27" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="K89" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="91" spans="9:27" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="L91" s="16" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="93" spans="9:27" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="M93" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="V93" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="94" spans="9:27" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="M94" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AA94" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="95" spans="9:27" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="M95" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="97" spans="9:12" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="K97" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="99" spans="9:12" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="L99" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="101" spans="9:12" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J101" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="103" spans="9:12" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="103" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A103" s="20">
+        <v>46105</v>
+      </c>
+      <c r="B103" s="9" t="s">
+        <v>145</v>
+      </c>
       <c r="I103" s="16" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="105" spans="9:12" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="105" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J105" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="107" spans="9:12" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="K106" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="107" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="K107" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="109" spans="9:12" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="109" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="K109" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="111" spans="9:12" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="111" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="L111" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="113" spans="9:22" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="I113" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="114" spans="9:22" ht="12" customHeight="1" x14ac:dyDescent="0.7">
@@ -4275,7 +4352,7 @@
     <row r="115" spans="9:22" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="I115" s="16"/>
       <c r="J115" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="116" spans="9:22" ht="12" customHeight="1" x14ac:dyDescent="0.7">
@@ -4284,7 +4361,7 @@
     <row r="117" spans="9:22" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="I117" s="16"/>
       <c r="K117" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="118" spans="9:22" ht="12" customHeight="1" x14ac:dyDescent="0.7">
@@ -4292,17 +4369,17 @@
     </row>
     <row r="119" spans="9:22" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="K119" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="121" spans="9:22" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="K121" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="122" spans="9:22" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="L122" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="124" spans="9:22" ht="12" customHeight="1" x14ac:dyDescent="0.7">
@@ -4323,7 +4400,7 @@
     </row>
     <row r="127" spans="9:22" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J127" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="V127" t="s">
         <v>45</v>
@@ -4331,10 +4408,10 @@
     </row>
     <row r="128" spans="9:22" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="I128" t="s">
+        <v>115</v>
+      </c>
+      <c r="U128" t="s">
         <v>116</v>
-      </c>
-      <c r="U128" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="129" spans="5:22" ht="12" customHeight="1" x14ac:dyDescent="0.7">
@@ -4363,10 +4440,10 @@
     </row>
     <row r="133" spans="5:22" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="I133" t="s">
+        <v>117</v>
+      </c>
+      <c r="U133" t="s">
         <v>118</v>
-      </c>
-      <c r="U133" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="134" spans="5:22" ht="12" customHeight="1" x14ac:dyDescent="0.7">
@@ -4420,7 +4497,7 @@
     </row>
     <row r="154" spans="5:8" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="H154" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="158" spans="5:8" ht="12" customHeight="1" x14ac:dyDescent="0.7">
@@ -4441,12 +4518,12 @@
     </row>
     <row r="164" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="I164" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="165" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J165" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="167" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
@@ -4469,25 +4546,25 @@
         <v>46073</v>
       </c>
       <c r="B171" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="J171" t="s">
         <v>138</v>
-      </c>
-      <c r="J171" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="173" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="E173" s="16" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="175" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="F175" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="177" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="G177" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="180" spans="2:7" s="12" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
@@ -4534,7 +4611,7 @@
     </row>
     <row r="205" spans="6:23" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="G205" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="207" spans="6:23" ht="12.75" customHeight="1" x14ac:dyDescent="0.7">
@@ -4545,19 +4622,19 @@
     <row r="208" spans="6:23" ht="12.75" customHeight="1" x14ac:dyDescent="0.7"/>
     <row r="209" spans="6:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.7">
       <c r="I209" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="210" spans="6:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.7"/>
     <row r="211" spans="6:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J211" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="212" spans="6:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.7"/>
     <row r="213" spans="6:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J213" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="214" spans="6:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.7"/>
@@ -4569,12 +4646,12 @@
     </row>
     <row r="218" spans="6:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="I218" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="220" spans="6:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J220" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="224" spans="6:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
@@ -4687,12 +4764,12 @@
     </row>
     <row r="257" spans="7:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J257" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="259" spans="7:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J259" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="260" spans="7:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
@@ -4702,13 +4779,13 @@
     </row>
     <row r="262" spans="7:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="G262" s="15" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H262" s="15"/>
     </row>
     <row r="264" spans="7:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="H264" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="266" spans="7:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
@@ -4718,12 +4795,12 @@
     </row>
     <row r="268" spans="7:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J268" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="270" spans="7:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="J270" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="271" spans="7:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
@@ -4733,23 +4810,23 @@
     </row>
     <row r="274" spans="2:8" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="F274" s="16" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="276" spans="2:8" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="G276" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="278" spans="2:8" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="H278" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="281" spans="2:8" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="B281" s="18"/>
       <c r="D281" s="19" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
